--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487013_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487013_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.349</v>
+        <v>3.592</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6143</v>
+        <v>1.7387</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7348</v>
+        <v>1.8533</v>
       </c>
       <c r="G2" t="n">
         <v>2.1153</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1758</v>
+        <v>-0.5812</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3093</v>
+        <v>0.4338</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1335</v>
+        <v>-1.0149</v>
       </c>
       <c r="V2" t="n">
         <v>0.0045</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0436</v>
+        <v>1.2402</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.4052</v>
+        <v>-1.4754</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4488</v>
+        <v>2.7156</v>
       </c>
       <c r="G3" t="n">
         <v>0.5237000000000001</v>
@@ -688,13 +688,13 @@
         <v>3.0801</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.6079</v>
+        <v>-1.4113</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5732</v>
+        <v>-0.6434</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0347</v>
+        <v>-0.7679</v>
       </c>
       <c r="V3" t="n">
         <v>0.0743</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5652</v>
+        <v>-0.0669</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7178</v>
+        <v>1.0975</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2829</v>
+        <v>-1.1644</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4543</v>
@@ -766,13 +766,13 @@
         <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1376</v>
+        <v>-0.6393</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5192</v>
+        <v>-0.1396</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6183</v>
+        <v>-0.4997</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8847</v>
+        <v>-1.5444</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.3873</v>
+        <v>-2.9877</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5026</v>
+        <v>1.4433</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5125</v>
@@ -844,13 +844,13 @@
         <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2312</v>
+        <v>0.5714</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9141</v>
+        <v>0.3136</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3171</v>
+        <v>0.2578</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1659</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9568</v>
+        <v>-1.7863</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2316</v>
+        <v>-2.0611</v>
       </c>
       <c r="F6" t="n">
         <v>0.2748</v>
@@ -922,10 +922,10 @@
         <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.616</v>
+        <v>-0.4456</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.527</v>
+        <v>-0.3565</v>
       </c>
       <c r="U6" t="n">
         <v>-0.0891</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1693</v>
+        <v>-2.3465</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4329</v>
+        <v>-2.7583</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2636</v>
+        <v>0.4118</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1131</v>
@@ -1000,13 +1000,13 @@
         <v>2.8748</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3581</v>
+        <v>-1.5353</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.039</v>
+        <v>-0.3644</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3191</v>
+        <v>-1.1709</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5195</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6685</v>
+        <v>-2.5433</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0457</v>
+        <v>-1.9798</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6228</v>
+        <v>-0.5635</v>
       </c>
       <c r="G8" t="n">
         <v>-2.5258</v>
@@ -1078,13 +1078,13 @@
         <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.964</v>
+        <v>-0.8389</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.651</v>
+        <v>-0.5851</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.313</v>
+        <v>-0.2537</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7948</v>
+        <v>-3.1004</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5274</v>
+        <v>-0.5661</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2675</v>
+        <v>-2.5343</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7754</v>
@@ -1156,13 +1156,13 @@
         <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3646</v>
+        <v>0.0591</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0464</v>
+        <v>0.0076</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3182</v>
+        <v>0.0514</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5893</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.37</v>
+        <v>-3.2523</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.888</v>
+        <v>-2.6517</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.482</v>
+        <v>-0.6006</v>
       </c>
       <c r="G10" t="n">
         <v>-2.269</v>
@@ -1234,13 +1234,13 @@
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6636</v>
+        <v>-1.5459</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9145</v>
+        <v>-0.6781</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7492</v>
+        <v>-0.8677</v>
       </c>
       <c r="V10" t="n">
         <v>1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6107</v>
+        <v>-4.2056</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8162</v>
+        <v>-3.6185</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7946</v>
+        <v>-0.5871</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3378</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3263</v>
+        <v>-0.9212</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0462</v>
+        <v>-0.8486</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2801</v>
+        <v>-0.0726</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1786</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. MERLO</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.2437</v>
+        <v>-5.9713</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.0177</v>
+        <v>-5.6035</v>
       </c>
       <c r="F12" t="n">
-        <v>0.774</v>
+        <v>-0.3678</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.0975</v>
+        <v>-6.3139</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.995</v>
+        <v>-3.7141</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1024</v>
+        <v>-2.5997</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.8934</v>
+        <v>-5.2624</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.972</v>
+        <v>-3.078</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9215</v>
+        <v>-2.1844</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.204</v>
+        <v>-1.0515</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0231</v>
+        <v>-0.6362</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1809</v>
+        <v>-0.4154</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4641</v>
+        <v>1.0267</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R12" t="n">
-        <v>3.4908</v>
+        <v>2.0534</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.157</v>
+        <v>-0.9987</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2289</v>
+        <v>0.2051</v>
       </c>
       <c r="U12" t="n">
-        <v>0.07199999999999999</v>
+        <v>-1.2038</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4534</v>
+        <v>0.3146</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1314</v>
+        <v>0.4805</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5848</v>
+        <v>-0.1659</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>S. MERLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.9877</v>
+        <v>-6.5566</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.6495</v>
+        <v>-6.8859</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3382</v>
+        <v>0.3294</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.3139</v>
+        <v>-7.0975</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.7141</v>
+        <v>-4.995</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5997</v>
+        <v>-2.1024</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.2624</v>
+        <v>-5.8934</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.078</v>
+        <v>-4.972</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.1844</v>
+        <v>-0.9215</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0515</v>
+        <v>-1.204</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6362</v>
+        <v>-0.0231</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4154</v>
+        <v>-1.1809</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0267</v>
+        <v>2.4641</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0534</v>
+        <v>3.4908</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.015</v>
+        <v>-0.4698</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8409</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1742</v>
+        <v>-0.3727</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3146</v>
+        <v>-1.4534</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4805</v>
+        <v>0.1314</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1659</v>
+        <v>-1.5848</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.8588</v>
+        <v>-26.5414</v>
       </c>
       <c r="E14" t="n">
-        <v>-29.0694</v>
+        <v>-27.7518</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2106</v>
+        <v>1.210499999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-24.1011</v>
@@ -1537,7 +1537,7 @@
         <v>-4.9699</v>
       </c>
       <c r="P14" t="n">
-        <v>9.240399999999999</v>
+        <v>9.240400000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.2937</v>
@@ -1546,13 +1546,13 @@
         <v>20.5341</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.0739</v>
+        <v>-8.756699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.0701</v>
+        <v>-2.752800000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.0039</v>
+        <v>-6.003800000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-2.924</v>
@@ -1561,7 +1561,7 @@
         <v>4.628100000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.5521</v>
+        <v>-7.552099999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.7276</v>
+        <v>6.8872</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0694</v>
+        <v>0.8602</v>
       </c>
       <c r="F15" t="n">
-        <v>6.6583</v>
+        <v>6.027</v>
       </c>
       <c r="G15" t="n">
         <v>4.3436</v>
@@ -1624,13 +1624,13 @@
         <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7947</v>
+        <v>2.9543</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2589</v>
+        <v>1.0497</v>
       </c>
       <c r="U15" t="n">
-        <v>2.5358</v>
+        <v>1.9046</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.8612</v>
+        <v>6.2108</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2579</v>
+        <v>4.0127</v>
       </c>
       <c r="F16" t="n">
-        <v>4.6033</v>
+        <v>2.1981</v>
       </c>
       <c r="G16" t="n">
-        <v>4.3184</v>
+        <v>5.5524</v>
       </c>
       <c r="H16" t="n">
-        <v>2.008</v>
+        <v>2.0794</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3105</v>
+        <v>3.473</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6732</v>
+        <v>4.3095</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8048999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8682</v>
+        <v>2.9596</v>
       </c>
       <c r="M16" t="n">
-        <v>2.6453</v>
+        <v>1.2429</v>
       </c>
       <c r="N16" t="n">
-        <v>1.203</v>
+        <v>0.7294</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4422</v>
+        <v>0.5134</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.616</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0534</v>
+        <v>-3.2855</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3374</v>
+        <v>0.5948</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6381</v>
+        <v>0.6314</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6992</v>
+        <v>-0.0366</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1786</v>
+        <v>2.117</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.3216</v>
+        <v>5.231</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6989</v>
+        <v>0.7935</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6227</v>
+        <v>4.4376</v>
       </c>
       <c r="G17" t="n">
-        <v>5.5524</v>
+        <v>4.3184</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0794</v>
+        <v>2.008</v>
       </c>
       <c r="I17" t="n">
-        <v>3.473</v>
+        <v>2.3105</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3095</v>
+        <v>1.6732</v>
       </c>
       <c r="K17" t="n">
-        <v>1.35</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9596</v>
+        <v>0.8682</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2429</v>
+        <v>2.6453</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7294</v>
+        <v>1.203</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5134</v>
+        <v>1.4422</v>
       </c>
       <c r="P17" t="n">
+        <v>-0.616</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-2.0534</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-3.2855</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2944</v>
+        <v>2.7073</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3176</v>
+        <v>1.1737</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.612</v>
+        <v>1.5336</v>
       </c>
       <c r="V17" t="n">
-        <v>2.117</v>
+        <v>-1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9452</v>
+        <v>4.5442</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8124</v>
+        <v>-0.0573</v>
       </c>
       <c r="F18" t="n">
-        <v>4.7576</v>
+        <v>4.6015</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6104</v>
+        <v>4.5229</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1053</v>
+        <v>1.5051</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5051</v>
+        <v>3.0178</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1239</v>
+        <v>1.5197</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0321</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0529</v>
+        <v>1.5518</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7343</v>
+        <v>3.0031</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1763</v>
+        <v>1.5372</v>
       </c>
       <c r="O18" t="n">
-        <v>1.5579</v>
+        <v>1.466</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8481</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.0801</v>
+        <v>-2.2588</v>
       </c>
       <c r="R18" t="n">
         <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0043</v>
+        <v>1.0481</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0272</v>
+        <v>0.6817</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0315</v>
+        <v>0.3664</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.867</v>
+        <v>4.0534</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6849</v>
+        <v>-2.3581</v>
       </c>
       <c r="F19" t="n">
-        <v>3.5519</v>
+        <v>6.4115</v>
       </c>
       <c r="G19" t="n">
-        <v>4.5229</v>
+        <v>4.8683</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5051</v>
+        <v>3.5712</v>
       </c>
       <c r="I19" t="n">
-        <v>3.0178</v>
+        <v>1.297</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5197</v>
+        <v>0.5785</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0321</v>
+        <v>1.421</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5518</v>
+        <v>-0.8425</v>
       </c>
       <c r="M19" t="n">
-        <v>3.0031</v>
+        <v>4.2898</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5372</v>
+        <v>2.1502</v>
       </c>
       <c r="O19" t="n">
-        <v>1.466</v>
+        <v>2.1396</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.0267</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2588</v>
+        <v>-4.3122</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2321</v>
+        <v>2.0534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6292</v>
+        <v>1.793</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0541</v>
+        <v>0.5461</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6833</v>
+        <v>1.2469</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8295</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3501</v>
+        <v>3.4456</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6133</v>
+        <v>-1.917</v>
       </c>
       <c r="F20" t="n">
-        <v>5.9634</v>
+        <v>5.3626</v>
       </c>
       <c r="G20" t="n">
-        <v>4.8683</v>
+        <v>3.6104</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5712</v>
+        <v>2.1053</v>
       </c>
       <c r="I20" t="n">
-        <v>1.297</v>
+        <v>1.5051</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5785</v>
+        <v>-0.1239</v>
       </c>
       <c r="K20" t="n">
-        <v>1.421</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8425</v>
+        <v>-0.0529</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2898</v>
+        <v>3.7343</v>
       </c>
       <c r="N20" t="n">
-        <v>2.1502</v>
+        <v>2.1763</v>
       </c>
       <c r="O20" t="n">
-        <v>2.1396</v>
+        <v>1.5579</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.2588</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.3122</v>
+        <v>-3.0801</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0534</v>
+        <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0897</v>
+        <v>0.5047</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7091</v>
+        <v>-0.1318</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7988</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3491</v>
+        <v>1.1786</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8295</v>
+        <v>1.4189</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.103</v>
+        <v>2.7655</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6459</v>
+        <v>2.1689</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4571</v>
+        <v>0.5966</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5019</v>
@@ -2092,13 +2092,13 @@
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4611</v>
+        <v>1.1236</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3176</v>
+        <v>0.8406</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1435</v>
+        <v>0.283</v>
       </c>
       <c r="V21" t="n">
         <v>1.5277</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0207</v>
+        <v>0.1923</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4365</v>
+        <v>-0.5797</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4572</v>
+        <v>0.772</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5154</v>
+        <v>-0.0605</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5288</v>
+        <v>0.4184</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9866</v>
+        <v>-0.4789</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6188</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4214</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1974</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1034</v>
+        <v>0.5579</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1074</v>
+        <v>0.4184</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2107</v>
+        <v>0.1395</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.8214</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5505</v>
+        <v>0.2528</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6464</v>
+        <v>0.0387</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0959</v>
+        <v>0.2141</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8070000000000001</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0013</v>
+        <v>-1.0184</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6843</v>
+        <v>-2.3779</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.3595</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0605</v>
+        <v>-1.5154</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4184</v>
+        <v>-0.5288</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4789</v>
+        <v>-0.9866</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-1.6188</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-0.4214</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-1.1974</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5579</v>
+        <v>0.1034</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4184</v>
+        <v>-0.1074</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1395</v>
+        <v>0.2107</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0593</v>
+        <v>0.5114</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0659</v>
+        <v>0.705</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1252</v>
+        <v>-0.1936</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.2177</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3365</v>
+        <v>-2.3609</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6513</v>
+        <v>-1.7559</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6852</v>
+        <v>-0.605</v>
       </c>
       <c r="G24" t="n">
         <v>-1.037</v>
@@ -2326,13 +2326,13 @@
         <v>0.2053</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7005</v>
+        <v>0.6761</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5733</v>
+        <v>0.4687</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1272</v>
+        <v>0.2074</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1786</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>27.8586</v>
+        <v>29.9507</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.210600000000001</v>
+        <v>-1.2106</v>
       </c>
       <c r="F25" t="n">
-        <v>29.0693</v>
+        <v>31.1614</v>
       </c>
       <c r="G25" t="n">
         <v>24.1012</v>
@@ -2392,7 +2392,7 @@
         <v>10.0687</v>
       </c>
       <c r="O25" t="n">
-        <v>8.264699999999998</v>
+        <v>8.264699999999999</v>
       </c>
       <c r="P25" t="n">
         <v>-9.240500000000001</v>
@@ -2404,13 +2404,13 @@
         <v>11.294</v>
       </c>
       <c r="S25" t="n">
-        <v>10.0739</v>
+        <v>12.1661</v>
       </c>
       <c r="T25" t="n">
         <v>6.0038</v>
       </c>
       <c r="U25" t="n">
-        <v>4.07</v>
+        <v>6.1624</v>
       </c>
       <c r="V25" t="n">
         <v>2.924</v>
